--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="478">
   <si>
     <t>Filename</t>
   </si>
@@ -808,658 +808,646 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9925,0.0016,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9899,0.0001,0.0001,0.0078</t>
-  </si>
-  <si>
-    <t>0.0615,0.0001,0.0000,0.9896</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9795,0.0017,0.0095,0.0013</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.9960,0.0001,0.0000,0.0017</t>
+  </si>
+  <si>
+    <t>0.0021,0.0004,0.0000,0.9994</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
+    <t>0.9993,0.0004,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.7350,0.0028,0.2311,0.0011</t>
-  </si>
-  <si>
-    <t>0.1050,0.0023,0.9422,0.0005</t>
-  </si>
-  <si>
-    <t>0.6223,0.0003,0.6065,0.0000</t>
-  </si>
-  <si>
-    <t>0.2402,0.0003,0.8188,0.0003</t>
-  </si>
-  <si>
-    <t>0.9237,0.0035,0.0390,0.0019</t>
+    <t>0.9565,0.0008,0.0408,0.0002</t>
+  </si>
+  <si>
+    <t>0.0394,0.0011,0.9727,0.0004</t>
+  </si>
+  <si>
+    <t>0.1033,0.0014,0.9398,0.0000</t>
+  </si>
+  <si>
+    <t>0.0073,0.0008,0.9934,0.0002</t>
+  </si>
+  <si>
+    <t>0.9861,0.0009,0.0093,0.0001</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9996,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0111,0.9904,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9974,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0251,0.0002,0.9697,0.0012</t>
-  </si>
-  <si>
-    <t>0.0027,0.0009,0.9954,0.0002</t>
-  </si>
-  <si>
-    <t>0.0051,0.0001,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9983,0.0004</t>
-  </si>
-  <si>
-    <t>0.0059,0.0006,0.9956,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0440,0.9605,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.8003,0.0868,0.0409,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.0047,0.9994,0.0093</t>
-  </si>
-  <si>
-    <t>0.0017,0.9886,0.0152,0.0008</t>
-  </si>
-  <si>
-    <t>0.9959,0.0030,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0027,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.5619,0.5357,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9963,0.0082,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.0488,0.9272,0.0093</t>
-  </si>
-  <si>
-    <t>0.0009,0.0004,0.9882,0.0340</t>
-  </si>
-  <si>
-    <t>0.0098,0.0041,0.9766,0.0009</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.9977,0.0008</t>
-  </si>
-  <si>
-    <t>0.0007,0.0040,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9968,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.9983,0.0009</t>
-  </si>
-  <si>
-    <t>0.0083,0.5372,0.0012,0.8883</t>
-  </si>
-  <si>
-    <t>0.0018,0.9937,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.9984,0.0165,0.0003</t>
+    <t>0.0007,0.9986,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0561,0.9653,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9993,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.1816,0.0002,0.8593,0.0005</t>
+  </si>
+  <si>
+    <t>0.0046,0.0016,0.9927,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9984,0.0008</t>
+  </si>
+  <si>
+    <t>0.0265,0.0002,0.9866,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0178,0.0000,0.9871,0.0004</t>
+  </si>
+  <si>
+    <t>0.3813,0.6152,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.9936,0.0036,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0027,0.9992,0.0212</t>
+  </si>
+  <si>
+    <t>0.0019,0.2722,0.9634,0.0006</t>
+  </si>
+  <si>
+    <t>0.9972,0.0018,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9540,0.0314,0.0067,0.0014</t>
+  </si>
+  <si>
+    <t>0.8619,0.1849,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0106,0.9683,0.0358,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.8158,0.1775,0.0102</t>
+  </si>
+  <si>
+    <t>0.0028,0.0013,0.9865,0.0113</t>
+  </si>
+  <si>
+    <t>0.0034,0.0015,0.9927,0.0004</t>
+  </si>
+  <si>
+    <t>0.3814,0.0002,0.7245,0.0003</t>
+  </si>
+  <si>
+    <t>0.0142,0.0052,0.9863,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9991,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0118,0.3409,0.0012,0.9395</t>
+  </si>
+  <si>
+    <t>0.0098,0.9697,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0125,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0015,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.6160,0.9944,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0079,0.0017,0.9874,0.0010</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0022,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0015,0.9978,0.0072</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9497,0.9646,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0015,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0069,0.9974,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9364,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9995,0.0016</t>
+  </si>
+  <si>
+    <t>0.0011,0.9987,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9111,0.0007,0.1329,0.0001</t>
+  </si>
+  <si>
+    <t>0.9133,0.0002,0.1321,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9996,0.0060</t>
+  </si>
+  <si>
+    <t>0.0002,0.9699,0.9357,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9909,0.8108,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9978,0.1282,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9844,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0000,0.0003,0.9988</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0012,0.9993</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9932,0.0222,0.0020</t>
+  </si>
+  <si>
+    <t>0.0001,0.9926,0.7120,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.8137,0.9626,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.4840,0.9936,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9818,0.9959,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9495,0.5780,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9995,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.9281,0.0019,0.0487,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2442,0.8444,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.5793,0.0116,0.2873,0.0018</t>
+  </si>
+  <si>
+    <t>0.4728,0.0003,0.6202,0.0002</t>
+  </si>
+  <si>
+    <t>0.8482,0.0210,0.0400,0.0025</t>
+  </si>
+  <si>
+    <t>0.7647,0.0396,0.0262,0.0072</t>
+  </si>
+  <si>
+    <t>0.0012,0.0013,0.1000,0.9712</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0079,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0004,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0011,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0050,0.9936,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9997,0.0001</t>
+    <t>0.0000,0.9999,0.0000,0.0211</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9258,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9995,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.4554,0.5317,0.0078,0.0002</t>
+  </si>
+  <si>
+    <t>0.4190,0.6344,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.1524,0.9859,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.6810,0.9860,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0012,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.9559,0.0003,0.0247,0.0021</t>
+  </si>
+  <si>
+    <t>0.5581,0.0005,0.5110,0.0004</t>
+  </si>
+  <si>
+    <t>0.0122,0.0000,0.9918,0.0002</t>
+  </si>
+  <si>
+    <t>0.0325,0.0003,0.9724,0.0004</t>
+  </si>
+  <si>
+    <t>0.0277,0.0000,0.0000,0.9963</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.6030,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0995,0.9180,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8159,0.2597,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.4851,0.0002,0.0022,0.6639</t>
+  </si>
+  <si>
+    <t>0.0010,0.0020,0.9941,0.0165</t>
+  </si>
+  <si>
+    <t>0.9824,0.0001,0.0027,0.0068</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0711,0.9178,0.0041,0.0026</t>
+  </si>
+  <si>
+    <t>0.9888,0.0044,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9169,0.0567,0.0042,0.0007</t>
+  </si>
+  <si>
+    <t>0.8489,0.0076,0.0956,0.0001</t>
+  </si>
+  <si>
+    <t>0.9708,0.0067,0.0107,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0021,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.5437,0.5433,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.5420,0.5468,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.2225,0.0411,0.7340,0.0005</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9998,0.0004</t>
+  </si>
+  <si>
+    <t>0.9697,0.0254,0.0023,0.0007</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0152,0.0155,0.9760,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.0079,0.9970,0.0015</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0014</t>
+  </si>
+  <si>
+    <t>0.0009,0.0007,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.1894,0.0049,0.8646,0.0007</t>
+  </si>
+  <si>
+    <t>0.0320,0.0071,0.9373,0.0027</t>
+  </si>
+  <si>
+    <t>0.0104,0.0012,0.9870,0.0002</t>
+  </si>
+  <si>
+    <t>0.0341,0.0186,0.9233,0.0003</t>
+  </si>
+  <si>
+    <t>0.1408,0.0018,0.8738,0.0002</t>
+  </si>
+  <si>
+    <t>0.6563,0.0013,0.2465,0.0107</t>
+  </si>
+  <si>
+    <t>0.0848,0.0037,0.9087,0.0009</t>
+  </si>
+  <si>
+    <t>0.0072,0.9923,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.9975,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0384,0.9738,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9546,0.0683,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.1484,0.8846,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0016,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9922,0.0016,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0234,0.0019,0.9785,0.0005</t>
+  </si>
+  <si>
+    <t>0.1480,0.0031,0.8296,0.0094</t>
+  </si>
+  <si>
+    <t>0.0021,0.0005,0.9966,0.0029</t>
+  </si>
+  <si>
+    <t>0.0032,0.0046,0.9903,0.0008</t>
+  </si>
+  <si>
+    <t>0.0014,0.0011,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.0125,0.0006,0.9851,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0024,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0026,0.9984,0.0013</t>
+  </si>
+  <si>
+    <t>0.0151,0.0111,0.9777,0.0025</t>
+  </si>
+  <si>
+    <t>0.4419,0.0039,0.5570,0.0068</t>
+  </si>
+  <si>
+    <t>0.0002,0.0008,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0020,0.9998,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.6943,0.9970,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.0001,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0018,0.9959,0.0006</t>
-  </si>
-  <si>
-    <t>0.9977,0.0016,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0140,0.9982,0.0022</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9869,0.9617,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0044,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0060,0.9983,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9291,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9993,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0002,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0017,0.9996,0.0035</t>
-  </si>
-  <si>
-    <t>0.0002,0.9610,0.8841,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9164,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.7894,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9915,0.9859,0.0000</t>
-  </si>
-  <si>
-    <t>0.0053,0.0001,0.0026,0.9962</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0009,0.9996</t>
-  </si>
-  <si>
-    <t>0.0006,0.0004,0.0005,0.9993</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9660,0.4485,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9965,0.8098,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9644,0.9605,0.0002</t>
-  </si>
-  <si>
-    <t>0.0028,0.0579,0.9697,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9915,0.9907,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9944,0.7133,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.0020,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.9647,0.0008,0.0156,0.0005</t>
-  </si>
-  <si>
-    <t>0.0051,0.0001,0.9957,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.5678,0.5897,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0283,0.0424,0.9533,0.0013</t>
-  </si>
-  <si>
-    <t>0.9281,0.0006,0.0884,0.0000</t>
-  </si>
-  <si>
-    <t>0.4775,0.1135,0.0582,0.0064</t>
-  </si>
-  <si>
-    <t>0.5713,0.0424,0.0799,0.0063</t>
-  </si>
-  <si>
-    <t>0.0008,0.0007,0.0038,0.9982</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0090,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0077</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9706,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9994,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.7110,0.1909,0.0168,0.0001</t>
-  </si>
-  <si>
-    <t>0.5029,0.5719,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0477,0.9956,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.2605,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0230,0.9881,0.0008</t>
-  </si>
-  <si>
-    <t>0.0017,0.0006,0.9959,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0003,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9879,0.0008,0.0061,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9980,0.0003</t>
-  </si>
-  <si>
-    <t>0.1637,0.0012,0.8560,0.0006</t>
-  </si>
-  <si>
-    <t>0.0489,0.0000,0.0000,0.9918</t>
-  </si>
-  <si>
-    <t>0.0000,0.0116,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9946,0.2882,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0323,0.9729,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9431,0.0999,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7599,0.0004,0.0079,0.1783</t>
-  </si>
-  <si>
-    <t>0.0015,0.0070,0.9867,0.0474</t>
-  </si>
-  <si>
-    <t>0.5754,0.0000,0.0251,0.1019</t>
-  </si>
-  <si>
-    <t>0.9967,0.0007,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.0138,0.9568,0.0163,0.0029</t>
-  </si>
-  <si>
-    <t>0.9820,0.0053,0.0058,0.0005</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.7830,0.2124,0.0017,0.0010</t>
-  </si>
-  <si>
-    <t>0.3611,0.0063,0.5839,0.0001</t>
-  </si>
-  <si>
-    <t>0.9505,0.0388,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9911,0.0066,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9297,0.0924,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.3029,0.7587,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.0066,0.0235,0.9907,0.0008</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.9583,0.0384,0.0021,0.0009</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0044,0.0090,0.9914,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.0171,0.9920,0.0008</t>
-  </si>
-  <si>
-    <t>0.0004,0.0012,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0105,0.0001,0.9957,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.0039,0.0009,0.9951,0.0002</t>
-  </si>
-  <si>
-    <t>0.0425,0.0017,0.9633,0.0006</t>
-  </si>
-  <si>
-    <t>0.0423,0.0166,0.9004,0.0024</t>
-  </si>
-  <si>
-    <t>0.0099,0.0013,0.9862,0.0003</t>
-  </si>
-  <si>
-    <t>0.0303,0.0074,0.9610,0.0002</t>
-  </si>
-  <si>
-    <t>0.3177,0.0059,0.6107,0.0002</t>
-  </si>
-  <si>
-    <t>0.3326,0.0018,0.6295,0.0032</t>
-  </si>
-  <si>
-    <t>0.1881,0.0022,0.8159,0.0004</t>
-  </si>
-  <si>
-    <t>0.0917,0.9239,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.9986,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4024,0.6930,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9949,0.0067,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7666,0.3646,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9887,0.0054,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9764,0.0016,0.0083,0.0013</t>
-  </si>
-  <si>
-    <t>0.4056,0.0083,0.5364,0.0013</t>
-  </si>
-  <si>
-    <t>0.0188,0.0008,0.9812,0.0009</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.9992,0.0025</t>
-  </si>
-  <si>
-    <t>0.0009,0.0041,0.9963,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.0022,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.0038,0.0013,0.9900,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0008,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0012,0.9986,0.0008</t>
-  </si>
-  <si>
-    <t>0.0105,0.0116,0.9775,0.0030</t>
-  </si>
-  <si>
-    <t>0.9773,0.0031,0.0125,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9998,0.0009</t>
-  </si>
-  <si>
-    <t>0.0007,0.0770,0.9939,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.0015,0.9945,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0013,0.9982,0.0035</t>
-  </si>
-  <si>
-    <t>0.2730,0.0084,0.5851,0.0020</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.9981,0.0009</t>
-  </si>
-  <si>
-    <t>0.9961,0.0002,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0017,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0064,0.0012,0.9906,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0295,0.9935,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0063,0.0013,0.9809,0.0059</t>
-  </si>
-  <si>
-    <t>0.0326,0.0053,0.9489,0.0029</t>
-  </si>
-  <si>
-    <t>0.0384,0.0004,0.9533,0.0014</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0014,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0071,0.0004,0.0003,0.9971</t>
-  </si>
-  <si>
-    <t>0.4419,0.0017,0.0000,0.5574</t>
+    <t>0.0002,0.0011,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0006,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0081,0.9961,0.0030</t>
+  </si>
+  <si>
+    <t>0.0378,0.0034,0.9435,0.0049</t>
+  </si>
+  <si>
+    <t>0.0214,0.0002,0.9806,0.0005</t>
+  </si>
+  <si>
+    <t>0.9961,0.0003,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2072,0.0025,0.7589,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0029,0.9952,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9991,0.0005</t>
+  </si>
+  <si>
+    <t>0.0033,0.0008,0.9940,0.0011</t>
+  </si>
+  <si>
+    <t>0.1146,0.0021,0.8553,0.0029</t>
+  </si>
+  <si>
+    <t>0.0116,0.0014,0.9734,0.0043</t>
+  </si>
+  <si>
+    <t>0.9780,0.0000,0.0001,0.0361</t>
+  </si>
+  <si>
+    <t>0.0001,0.0015,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0073,0.0001,0.0005,0.9973</t>
+  </si>
+  <si>
+    <t>0.5793,0.0014,0.0005,0.4313</t>
   </si>
 </sst>
 </file>
@@ -1845,7 +1833,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1859,7 +1847,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1873,7 +1861,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1887,7 +1875,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1901,7 +1889,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1915,7 +1903,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1929,7 +1917,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1943,7 +1931,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1957,7 +1945,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1971,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1985,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1999,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2013,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2027,7 +2015,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2041,7 +2029,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2055,7 +2043,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2069,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2083,7 +2071,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2097,7 +2085,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2111,7 +2099,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2125,7 +2113,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2139,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2153,7 +2141,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2167,7 +2155,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2181,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2195,7 +2183,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2209,7 +2197,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2223,7 +2211,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2237,7 +2225,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2251,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2265,7 +2253,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2279,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2290,10 +2278,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2307,7 +2295,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2321,7 +2309,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2332,10 +2320,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2349,7 +2337,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2360,10 +2348,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2377,7 +2365,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2391,7 +2379,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2405,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2419,7 +2407,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2433,7 +2421,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2447,7 +2435,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2458,10 +2446,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2475,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2489,7 +2477,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2503,7 +2491,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2517,7 +2505,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2528,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2545,7 +2533,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2559,7 +2547,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2573,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2587,7 +2575,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2601,7 +2589,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2615,7 +2603,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2657,7 +2645,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>274</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2671,7 +2659,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2685,7 +2673,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2699,7 +2687,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2713,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2727,7 +2715,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2741,7 +2729,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2755,7 +2743,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2769,7 +2757,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2783,7 +2771,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>278</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2864,7 +2852,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>333</v>
@@ -3063,7 +3051,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>270</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3091,7 +3079,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>274</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3119,7 +3107,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3133,7 +3121,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3147,7 +3135,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3161,7 +3149,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3175,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3189,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3203,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3217,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3231,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3245,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3273,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3287,7 +3275,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3301,7 +3289,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3315,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3329,7 +3317,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3343,7 +3331,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3357,7 +3345,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3371,7 +3359,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3385,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3399,7 +3387,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>359</v>
+        <v>280</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3413,7 +3401,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3427,7 +3415,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3438,10 +3426,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3452,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3469,7 +3457,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3483,7 +3471,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3497,7 +3485,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3511,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3525,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3539,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3553,7 +3541,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3567,7 +3555,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3578,10 +3566,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3595,7 +3583,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3609,7 +3597,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>270</v>
+        <v>372</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3623,7 +3611,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3637,7 +3625,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3651,7 +3639,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3665,7 +3653,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3679,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3693,7 +3681,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3707,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3721,7 +3709,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3732,10 +3720,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3749,7 +3737,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3763,7 +3751,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3777,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3788,10 +3776,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3805,7 +3793,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3819,7 +3807,7 @@
         <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3833,7 +3821,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3861,7 +3849,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3875,7 +3863,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3886,10 +3874,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3903,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3917,7 +3905,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3931,7 +3919,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3945,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3959,7 +3947,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3970,10 +3958,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3987,7 +3975,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4001,7 +3989,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4015,7 +4003,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4029,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4043,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4057,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4071,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4085,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4096,10 +4084,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4113,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4127,7 +4115,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4141,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4155,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4169,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4183,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>391</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4197,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4211,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>270</v>
+        <v>376</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4225,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>270</v>
+        <v>376</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4239,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4250,10 +4238,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D174" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4264,10 +4252,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4281,7 +4269,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4295,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4309,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4323,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4407,7 +4395,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>420</v>
+        <v>313</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4421,7 +4409,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4435,7 +4423,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4449,7 +4437,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4463,7 +4451,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4477,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4491,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4505,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4519,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4533,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4547,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4558,10 +4546,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4575,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4589,7 +4577,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4603,7 +4591,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4617,7 +4605,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4631,7 +4619,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4642,10 +4630,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4659,7 +4647,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4673,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4687,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4701,7 +4689,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4715,7 +4703,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4729,7 +4717,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4743,7 +4731,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4757,7 +4745,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4771,7 +4759,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4785,7 +4773,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4799,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>270</v>
+        <v>373</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4813,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>448</v>
+        <v>270</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4827,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4841,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4855,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4869,7 +4857,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>272</v>
+        <v>372</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4883,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>270</v>
+        <v>450</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4897,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>452</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4911,7 +4899,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4925,7 +4913,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4936,10 +4924,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4953,7 +4941,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4967,7 +4955,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4978,10 +4966,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4995,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5009,7 +4997,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5023,7 +5011,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5037,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5051,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5065,7 +5053,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5079,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5093,7 +5081,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5107,7 +5095,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5121,7 +5109,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>272</v>
+        <v>465</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5135,7 +5123,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5149,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>467</v>
+        <v>376</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5163,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>451</v>
+        <v>274</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5177,7 +5165,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>468</v>
+        <v>372</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5191,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5205,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5219,7 +5207,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5233,7 +5221,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5247,7 +5235,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5261,7 +5249,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5275,7 +5263,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5289,7 +5277,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5303,7 +5291,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5317,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5331,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5345,7 +5333,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5359,7 +5347,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5387,7 +5375,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5398,10 +5386,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
